--- a/NY_State_Reports_2026-10-16/FanDuel_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-16/FanDuel_Weekly_Report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7952089D-AD47-4728-94A9-4F395AB77923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2C97C6-5D3F-4953-BFC4-CCD7BB8E59A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
   <sheets>
     <sheet name="FY 26-27" sheetId="7" r:id="rId1"/>
@@ -2854,7 +2854,12 @@
         <v>46306</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="F41" s="22"/>
+      <c r="C41" s="20">
+        <v>209285806.87999997</v>
+      </c>
+      <c r="F41" s="22">
+        <v>19123120.310000002</v>
+      </c>
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
@@ -3395,11 +3400,11 @@
       </c>
       <c r="C67" s="23">
         <f>SUM(C13:C66)</f>
-        <v>4871222114.9400005</v>
+        <v>5080507921.8200006</v>
       </c>
       <c r="F67" s="35">
         <f>SUM(F13:F66)</f>
-        <v>486904277.17050016</v>
+        <v>506027397.48050016</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
